--- a/IT23543478_Test cases.xlsx
+++ b/IT23543478_Test cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gima\Desktop\IT23543478\IT23543478_project_playwright\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51C93FE-CE0D-4104-B2E7-6D73EBAA0D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A7F4B9-1462-410A-A47D-993D081BB906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2248,15 +2248,15 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Iskoola Pota"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="8"/>
       <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -2325,32 +2325,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2633,18 +2631,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H123"/>
-  <sheetFormatPr defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
-    <col min="4" max="4" width="25.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.5546875" customWidth="1"/>
-    <col min="7" max="7" width="25.44140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="50.44140625" style="4" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="7"/>
+    <col min="3" max="3" width="22.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="22.5546875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="7"/>
+    <col min="7" max="7" width="25.44140625" style="12" customWidth="1"/>
+    <col min="8" max="8" width="50.44140625" style="12" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" style="7" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2670,2137 +2671,2368 @@
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="3" t="s">
+    <row r="3" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+    <row r="4" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="3" t="s">
+    <row r="6" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="2" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+    <row r="7" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="2" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+    <row r="9" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="2" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+    <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+    <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="3" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="3" t="s">
+    <row r="15" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="3" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+    <row r="16" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="2" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="3" t="s">
+    <row r="18" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="2" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+    <row r="19" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="H20" s="2" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+    <row r="21" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="H22" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
+    <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
+    <row r="25" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="H26" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="3" t="s">
+    <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="2" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-    </row>
-    <row r="29" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
+    <row r="28" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H29" s="2" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="3" t="s">
+    <row r="30" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H30" s="2" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-    </row>
-    <row r="32" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="s">
+    <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H32" s="2" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
+    <row r="33" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H34" s="2" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="3" t="s">
+    <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H35" s="2" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-    </row>
-    <row r="37" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="s">
+    <row r="36" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="F37" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H37" s="2" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-    </row>
-    <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="11" t="s">
+    <row r="38" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H39" s="2" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
+    <row r="40" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H41" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="11" t="s">
+    <row r="42" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F43" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="H43" s="2" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-    </row>
-    <row r="45" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="11" t="s">
+    <row r="44" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F45" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H45" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-    </row>
-    <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="11" t="s">
+    <row r="46" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="2" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-    </row>
-    <row r="49" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="11" t="s">
+    <row r="48" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="F49" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="H49" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="3" t="s">
+    <row r="50" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H50" s="3" t="s">
+      <c r="H50" s="2" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="11" t="s">
+    <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+    </row>
+    <row r="52" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F52" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="G52" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="H52" s="2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="7"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="3" t="s">
+    <row r="53" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="H53" s="2" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-    </row>
-    <row r="55" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="11" t="s">
+    <row r="54" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="F55" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="G55" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="H55" s="2" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-    </row>
-    <row r="57" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="11" t="s">
+    <row r="56" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+    </row>
+    <row r="57" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="H57" s="2" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="7"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-    </row>
-    <row r="59" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="11" t="s">
+    <row r="58" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="8"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+    </row>
+    <row r="59" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E59" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F59" s="9" t="s">
+      <c r="F59" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="G59" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="H59" s="3" t="s">
+      <c r="H59" s="2" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="7"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-    </row>
-    <row r="61" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="11" t="s">
+    <row r="60" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="8"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="F61" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="H61" s="5" t="s">
+      <c r="H61" s="3" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="7"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-    </row>
-    <row r="63" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="11" t="s">
+    <row r="62" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="8"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D63" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="E63" s="10" t="s">
+      <c r="E63" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="F63" s="9" t="s">
+      <c r="F63" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="G63" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="H63" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="7"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-    </row>
-    <row r="65" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="11" t="s">
+    <row r="64" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+    </row>
+    <row r="65" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E65" s="10" t="s">
+      <c r="E65" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="F65" s="9" t="s">
+      <c r="F65" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="H65" s="3" t="s">
+      <c r="H65" s="2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-    </row>
-    <row r="67" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="11" t="s">
+    <row r="66" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="E67" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="F67" s="9" t="s">
+      <c r="F67" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="H67" s="5" t="s">
+      <c r="H67" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-    </row>
-    <row r="69" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="11" t="s">
+    <row r="68" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+    </row>
+    <row r="69" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="D69" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="E69" s="10" t="s">
+      <c r="E69" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="F69" s="9" t="s">
+      <c r="F69" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G69" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="H69" s="3" t="s">
+      <c r="H69" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="7"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-    </row>
-    <row r="71" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="11" t="s">
+    <row r="70" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+    </row>
+    <row r="71" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F71" s="9" t="s">
+      <c r="F71" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G71" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="H71" s="3" t="s">
+      <c r="H71" s="2" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-    </row>
-    <row r="73" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="11" t="s">
+    <row r="72" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="8"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D73" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="E73" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="F73" s="9" t="s">
+      <c r="F73" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="G73" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="H73" s="3" t="s">
+      <c r="H73" s="2" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-    </row>
-    <row r="75" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="11" t="s">
+    <row r="74" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="8"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+    </row>
+    <row r="75" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D75" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="E75" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="F75" s="9" t="s">
+      <c r="F75" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="G75" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="H75" s="3" t="s">
+      <c r="H75" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="7"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="3" t="s">
+    <row r="76" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="8"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="H76" s="5" t="s">
+      <c r="H76" s="3" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="5"/>
-    </row>
-    <row r="78" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="11" t="s">
+    <row r="77" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="11"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="3"/>
+    </row>
+    <row r="78" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D78" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E78" s="10" t="s">
+      <c r="E78" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="F78" s="9" t="s">
+      <c r="F78" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G78" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="H78" s="2" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="7"/>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-    </row>
-    <row r="80" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="11" t="s">
+    <row r="79" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="8"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+    </row>
+    <row r="80" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D80" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="E80" s="10" t="s">
+      <c r="E80" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="F80" s="9" t="s">
+      <c r="F80" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="G80" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="H80" s="5" t="s">
+      <c r="H80" s="3" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="7"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-    </row>
-    <row r="82" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="11" t="s">
+    <row r="81" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="8"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+    </row>
+    <row r="82" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E82" s="10" t="s">
+      <c r="E82" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="F82" s="9" t="s">
+      <c r="F82" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G82" s="3" t="s">
+      <c r="G82" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="H82" s="3" t="s">
+      <c r="H82" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="7"/>
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-    </row>
-    <row r="84" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="11" t="s">
+    <row r="83" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="8"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+    </row>
+    <row r="84" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="E84" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F84" s="9" t="s">
+      <c r="F84" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="G84" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="H84" s="3" t="s">
+      <c r="H84" s="2" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="7"/>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-    </row>
-    <row r="86" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="11" t="s">
+    <row r="85" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="8"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+    </row>
+    <row r="86" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="E86" s="10" t="s">
+      <c r="E86" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F86" s="9" t="s">
+      <c r="F86" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G86" s="3" t="s">
+      <c r="G86" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="H86" s="3" t="s">
+      <c r="H86" s="2" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="7"/>
-      <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-    </row>
-    <row r="88" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="11" t="s">
+    <row r="87" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="8"/>
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+    </row>
+    <row r="88" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D88" s="12" t="s">
+      <c r="D88" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E88" s="10" t="s">
+      <c r="E88" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="F88" s="9" t="s">
+      <c r="F88" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="G88" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="H88" s="3" t="s">
+      <c r="H88" s="2" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="7"/>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-    </row>
-    <row r="90" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="11" t="s">
+    <row r="89" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="8"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+    </row>
+    <row r="90" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E90" s="10" t="s">
+      <c r="E90" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F90" s="9" t="s">
+      <c r="F90" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="G90" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="H90" s="3" t="s">
+      <c r="H90" s="2" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="7"/>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-    </row>
-    <row r="92" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="11" t="s">
+    <row r="91" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="8"/>
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+    </row>
+    <row r="92" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D92" s="12" t="s">
+      <c r="D92" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E92" s="10" t="s">
+      <c r="E92" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F92" s="9" t="s">
+      <c r="F92" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G92" s="3" t="s">
+      <c r="G92" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="H92" s="3" t="s">
+      <c r="H92" s="2" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="7"/>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-    </row>
-    <row r="94" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="11" t="s">
+    <row r="93" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="8"/>
+      <c r="B93" s="8"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+    </row>
+    <row r="94" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B94" s="9" t="s">
+      <c r="B94" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D94" s="12" t="s">
+      <c r="D94" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="E94" s="10" t="s">
+      <c r="E94" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F94" s="9" t="s">
+      <c r="F94" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G94" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="H94" s="2" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="7"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-    </row>
-    <row r="96" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="11" t="s">
+    <row r="95" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="8"/>
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+    </row>
+    <row r="96" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="D96" s="12" t="s">
+      <c r="D96" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="E96" s="10" t="s">
+      <c r="E96" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F96" s="9" t="s">
+      <c r="F96" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="G96" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="H96" s="2" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="7"/>
-      <c r="B97" s="7"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="3" t="s">
+    <row r="97" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="8"/>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="H97" s="3" t="s">
+      <c r="H97" s="2" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-    </row>
-    <row r="99" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="11" t="s">
+    <row r="98" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="11"/>
+      <c r="B98" s="11"/>
+      <c r="C98" s="11"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
+      <c r="F98" s="11"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+    </row>
+    <row r="99" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="B99" s="9" t="s">
+      <c r="B99" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D99" s="12" t="s">
+      <c r="D99" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E99" s="10" t="s">
+      <c r="E99" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F99" s="9" t="s">
+      <c r="F99" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G99" s="3" t="s">
+      <c r="G99" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="H99" s="3" t="s">
+      <c r="H99" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="7"/>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="3" t="s">
+    <row r="100" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="8"/>
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="H100" s="3" t="s">
+      <c r="H100" s="2" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-    </row>
-    <row r="102" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="11" t="s">
+    <row r="101" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="11"/>
+      <c r="B101" s="11"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
+      <c r="F101" s="11"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+    </row>
+    <row r="102" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B102" s="9" t="s">
+      <c r="B102" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="D102" s="12" t="s">
+      <c r="D102" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="E102" s="10" t="s">
+      <c r="E102" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="F102" s="9" t="s">
+      <c r="F102" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G102" s="3" t="s">
+      <c r="G102" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="H102" s="5" t="s">
+      <c r="H102" s="3" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="7"/>
-      <c r="B103" s="7"/>
-      <c r="C103" s="7"/>
-      <c r="D103" s="7"/>
-      <c r="E103" s="7"/>
-      <c r="F103" s="7"/>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
-    </row>
-    <row r="104" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="11" t="s">
+    <row r="103" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="8"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+    </row>
+    <row r="104" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B104" s="9" t="s">
+      <c r="B104" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D104" s="12" t="s">
+      <c r="D104" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="E104" s="10" t="s">
+      <c r="E104" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F104" s="9" t="s">
+      <c r="F104" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G104" s="3" t="s">
+      <c r="G104" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="H104" s="5" t="s">
+      <c r="H104" s="3" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="7"/>
-      <c r="B105" s="7"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
-      <c r="G105" s="3" t="s">
+    <row r="105" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="8"/>
+      <c r="B105" s="8"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="8"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="H105" s="3" t="s">
+      <c r="H105" s="2" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="2"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="3"/>
-      <c r="H106" s="3"/>
-    </row>
-    <row r="107" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="11" t="s">
+    <row r="106" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="11"/>
+      <c r="B106" s="11"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="11"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+    </row>
+    <row r="107" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="B107" s="9" t="s">
+      <c r="B107" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D107" s="12" t="s">
+      <c r="D107" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E107" s="10" t="s">
+      <c r="E107" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="F107" s="9" t="s">
+      <c r="F107" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G107" s="3" t="s">
+      <c r="G107" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="H107" s="5" t="s">
+      <c r="H107" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="7"/>
-      <c r="B108" s="7"/>
-      <c r="C108" s="7"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7"/>
-      <c r="G108" s="3" t="s">
+    <row r="108" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="8"/>
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="8"/>
+      <c r="F108" s="8"/>
+      <c r="G108" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="H108" s="3" t="s">
+      <c r="H108" s="2" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="7"/>
-      <c r="B109" s="7"/>
-      <c r="C109" s="7"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7"/>
-      <c r="G109" s="3" t="s">
+    <row r="109" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="8"/>
+      <c r="B109" s="8"/>
+      <c r="C109" s="8"/>
+      <c r="D109" s="8"/>
+      <c r="E109" s="8"/>
+      <c r="F109" s="8"/>
+      <c r="G109" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="H109" s="5" t="s">
+      <c r="H109" s="3" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="8"/>
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-    </row>
-    <row r="111" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="11" t="s">
+    <row r="110" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="10"/>
+      <c r="B110" s="10"/>
+      <c r="C110" s="10"/>
+      <c r="D110" s="10"/>
+      <c r="E110" s="10"/>
+      <c r="F110" s="10"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+    </row>
+    <row r="111" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B111" s="9" t="s">
+      <c r="B111" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D111" s="12" t="s">
+      <c r="D111" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E111" s="10" t="s">
+      <c r="E111" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="F111" s="9" t="s">
+      <c r="F111" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G111" s="3" t="s">
+      <c r="G111" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="H111" s="3" t="s">
+      <c r="H111" s="2" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="7"/>
-      <c r="B112" s="7"/>
-      <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="7"/>
-      <c r="G112" s="3" t="s">
+    <row r="112" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="8"/>
+      <c r="B112" s="8"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="8"/>
+      <c r="E112" s="8"/>
+      <c r="F112" s="8"/>
+      <c r="G112" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="H112" s="3" t="s">
+      <c r="H112" s="2" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="8"/>
-      <c r="B113" s="8"/>
-      <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8"/>
-      <c r="F113" s="8"/>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
-    </row>
-    <row r="114" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="11" t="s">
+    <row r="113" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="10"/>
+      <c r="B113" s="10"/>
+      <c r="C113" s="10"/>
+      <c r="D113" s="10"/>
+      <c r="E113" s="10"/>
+      <c r="F113" s="10"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+    </row>
+    <row r="114" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B114" s="9" t="s">
+      <c r="B114" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="D114" s="12" t="s">
+      <c r="D114" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="E114" s="10" t="s">
+      <c r="E114" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="F114" s="9" t="s">
+      <c r="F114" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G114" s="3" t="s">
+      <c r="G114" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="H114" s="3" t="s">
+      <c r="H114" s="2" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="7"/>
-      <c r="B115" s="7"/>
-      <c r="C115" s="7"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
-      <c r="G115" s="3" t="s">
+    <row r="115" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="8"/>
+      <c r="B115" s="8"/>
+      <c r="C115" s="8"/>
+      <c r="D115" s="8"/>
+      <c r="E115" s="8"/>
+      <c r="F115" s="8"/>
+      <c r="G115" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="H115" s="3" t="s">
+      <c r="H115" s="2" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="7"/>
-      <c r="B116" s="7"/>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="3" t="s">
+    <row r="116" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="8"/>
+      <c r="B116" s="8"/>
+      <c r="C116" s="8"/>
+      <c r="D116" s="8"/>
+      <c r="E116" s="8"/>
+      <c r="F116" s="8"/>
+      <c r="G116" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="H116" s="3" t="s">
+      <c r="H116" s="2" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="7"/>
-      <c r="B117" s="7"/>
-      <c r="C117" s="7"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-      <c r="G117" s="3" t="s">
+    <row r="117" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="8"/>
+      <c r="B117" s="8"/>
+      <c r="C117" s="8"/>
+      <c r="D117" s="8"/>
+      <c r="E117" s="8"/>
+      <c r="F117" s="8"/>
+      <c r="G117" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H117" s="3" t="s">
+      <c r="H117" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="7"/>
-      <c r="B118" s="7"/>
-      <c r="C118" s="7"/>
-      <c r="D118" s="7"/>
-      <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
-      <c r="G118" s="3" t="s">
+    <row r="118" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="8"/>
+      <c r="B118" s="8"/>
+      <c r="C118" s="8"/>
+      <c r="D118" s="8"/>
+      <c r="E118" s="8"/>
+      <c r="F118" s="8"/>
+      <c r="G118" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="H118" s="3" t="s">
+      <c r="H118" s="2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="8"/>
-      <c r="B119" s="8"/>
-      <c r="C119" s="8"/>
-      <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="8"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-    </row>
-    <row r="120" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="11" t="s">
+    <row r="119" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="10"/>
+      <c r="B119" s="10"/>
+      <c r="C119" s="10"/>
+      <c r="D119" s="10"/>
+      <c r="E119" s="10"/>
+      <c r="F119" s="10"/>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+    </row>
+    <row r="120" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B120" s="9" t="s">
+      <c r="B120" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="D120" s="12" t="s">
+      <c r="D120" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E120" s="10" t="s">
+      <c r="E120" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F120" s="9" t="s">
+      <c r="F120" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G120" s="3" t="s">
+      <c r="G120" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="H120" s="3" t="s">
+      <c r="H120" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="7"/>
-      <c r="B121" s="7"/>
-      <c r="C121" s="7"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="7"/>
-      <c r="G121" s="3" t="s">
+    <row r="121" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="8"/>
+      <c r="B121" s="8"/>
+      <c r="C121" s="8"/>
+      <c r="D121" s="8"/>
+      <c r="E121" s="8"/>
+      <c r="F121" s="8"/>
+      <c r="G121" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H121" s="3" t="s">
+      <c r="H121" s="2" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="7"/>
-      <c r="B122" s="7"/>
-      <c r="C122" s="7"/>
-      <c r="D122" s="7"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
-      <c r="G122" s="3" t="s">
+    <row r="122" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="8"/>
+      <c r="B122" s="8"/>
+      <c r="C122" s="8"/>
+      <c r="D122" s="8"/>
+      <c r="E122" s="8"/>
+      <c r="F122" s="8"/>
+      <c r="G122" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="H122" s="3" t="s">
+      <c r="H122" s="2" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="8"/>
-      <c r="B123" s="8"/>
-      <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="8"/>
-      <c r="G123" s="3"/>
-      <c r="H123" s="3"/>
+    <row r="123" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="10"/>
+      <c r="B123" s="10"/>
+      <c r="C123" s="10"/>
+      <c r="D123" s="10"/>
+      <c r="E123" s="10"/>
+      <c r="F123" s="10"/>
+      <c r="G123" s="2"/>
+      <c r="H123" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="300">
-    <mergeCell ref="A120:A123"/>
-    <mergeCell ref="F114:F119"/>
-    <mergeCell ref="C120:C123"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="F71:F72"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="F63:F64"/>
-    <mergeCell ref="A111:A113"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="F107:F110"/>
-    <mergeCell ref="C111:C113"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="E52:E54"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="D120:D123"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="F120:F123"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="F86:F87"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="F59:F60"/>
+    <mergeCell ref="A114:A119"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B107:B110"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="E99:E100"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="F84:F85"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="E86:E87"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="F102:F103"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E67:E68"/>
+    <mergeCell ref="E96:E97"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="B120:B123"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="F104:F105"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="F94:F95"/>
+    <mergeCell ref="E120:E123"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="F92:F93"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="F80:F81"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="D49:D51"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="F49:F51"/>
+    <mergeCell ref="E75:E76"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="F75:F76"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="F88:F89"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="F90:F91"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="D114:D119"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="E92:E93"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="D107:D110"/>
+    <mergeCell ref="E94:E95"/>
+    <mergeCell ref="F111:F113"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="E102:E103"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="E111:E113"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="F67:F68"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="B114:B119"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="F78:F79"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="C107:C110"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E82:E83"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="C99:C100"/>
+    <mergeCell ref="F96:F97"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="E107:E110"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="C17:C19"/>
     <mergeCell ref="D111:D113"/>
@@ -4825,261 +5057,30 @@
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="C39:C40"/>
     <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A120:A123"/>
+    <mergeCell ref="F114:F119"/>
+    <mergeCell ref="C120:C123"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="F71:F72"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="F63:F64"/>
+    <mergeCell ref="A111:A113"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="F107:F110"/>
+    <mergeCell ref="C111:C113"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="D67:D68"/>
+    <mergeCell ref="B88:B89"/>
     <mergeCell ref="C114:C119"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="C107:C110"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="E82:E83"/>
     <mergeCell ref="E114:E119"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="F69:F70"/>
-    <mergeCell ref="C99:C100"/>
-    <mergeCell ref="F96:F97"/>
-    <mergeCell ref="B80:B81"/>
     <mergeCell ref="B111:B113"/>
-    <mergeCell ref="D114:D119"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="E92:E93"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="D107:D110"/>
-    <mergeCell ref="E94:E95"/>
-    <mergeCell ref="F111:F113"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="E102:E103"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="E111:E113"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="F67:F68"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="B114:B119"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="F78:F79"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="F88:F89"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="F90:F91"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="F34:F36"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="B120:B123"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="F104:F105"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="D65:D66"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="F94:F95"/>
-    <mergeCell ref="E120:E123"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="F92:F93"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E67:E68"/>
-    <mergeCell ref="E96:E97"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="F84:F85"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="E86:E87"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="F102:F103"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E107:E110"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="A114:A119"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B107:B110"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="E99:E100"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="D120:D123"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="F120:F123"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D99:D100"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="F86:F87"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="E65:E66"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="F59:F60"/>
-    <mergeCell ref="F29:F31"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="D49:D51"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="F49:F51"/>
-    <mergeCell ref="E75:E76"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="F75:F76"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="E52:E54"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B92:B93"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
